--- a/data/trans_dic/P25A$preocupacion-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,91</t>
+          <t>3,77; 8,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,17</t>
+          <t>3,9; 9,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,92</t>
+          <t>5,13; 12,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 9,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 11,7</t>
+          <t>1,36; 11,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 27,0</t>
+          <t>5,13; 27,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,35</t>
+          <t>3,44; 8,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,44</t>
+          <t>3,79; 8,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 13,37</t>
+          <t>5,92; 13,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,32</t>
+          <t>5,45; 13,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,24</t>
+          <t>5,86; 12,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 17,35</t>
+          <t>8,86; 17,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 16,39</t>
+          <t>6,22; 16,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 12,74</t>
+          <t>4,75; 12,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 10,15</t>
+          <t>3,35; 10,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 12,68</t>
+          <t>6,8; 12,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,34</t>
+          <t>6,28; 11,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,07</t>
+          <t>7,33; 13,04</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 18,1</t>
+          <t>5,51; 18,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 16,79</t>
+          <t>4,46; 17,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 28,26</t>
+          <t>9,85; 27,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 18,67</t>
+          <t>2,24; 17,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 19,65</t>
+          <t>5,34; 20,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,81</t>
+          <t>5,32; 18,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 15,48</t>
+          <t>4,99; 14,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 15,82</t>
+          <t>6,39; 16,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 20,14</t>
+          <t>9,04; 21,28</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,94</t>
+          <t>5,66; 10,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,94</t>
+          <t>5,93; 9,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,86</t>
+          <t>9,27; 14,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,65</t>
+          <t>4,89; 12,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,3</t>
+          <t>5,37; 11,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,71; 11,91</t>
+          <t>5,62; 11,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,87</t>
+          <t>6,03; 9,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,77</t>
+          <t>6,35; 9,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 12,78</t>
+          <t>8,66; 12,67</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10858; 27007</t>
+          <t>11428; 27148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14573; 34108</t>
+          <t>14529; 35227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10430; 27115</t>
+          <t>10760; 26604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5029</t>
+          <t>0; 4686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>931; 8082</t>
+          <t>943; 8184</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1938; 10160</t>
+          <t>1929; 10222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11774; 29324</t>
+          <t>12095; 29239</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16589; 37251</t>
+          <t>16718; 37921</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14392; 33090</t>
+          <t>14651; 32428</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13077; 31567</t>
+          <t>12924; 31291</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21169; 42574</t>
+          <t>20361; 43778</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28440; 52390</t>
+          <t>26764; 52113</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9152; 24788</t>
+          <t>9410; 25089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11377; 30598</t>
+          <t>11395; 30372</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6604; 20410</t>
+          <t>6728; 21025</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26312; 49242</t>
+          <t>26395; 50176</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37744; 66656</t>
+          <t>36933; 66521</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37518; 65745</t>
+          <t>36874; 65585</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4551; 15279</t>
+          <t>4653; 15834</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4135; 16165</t>
+          <t>4292; 16778</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8944; 25325</t>
+          <t>8829; 24667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1150; 9587</t>
+          <t>1151; 8881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4033; 15208</t>
+          <t>4137; 15864</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5501; 16930</t>
+          <t>5056; 17371</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6827; 21026</t>
+          <t>6775; 20349</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11474; 27482</t>
+          <t>11096; 27953</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17050; 37201</t>
+          <t>16697; 39307</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36167; 62083</t>
+          <t>35340; 63240</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48967; 81135</t>
+          <t>48425; 80815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55487; 89362</t>
+          <t>55773; 90145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13204; 31723</t>
+          <t>12250; 30475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21379; 43687</t>
+          <t>20743; 43260</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19049; 39737</t>
+          <t>18750; 39519</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53133; 86402</t>
+          <t>52820; 86850</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76504; 117461</t>
+          <t>76378; 117202</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81931; 119536</t>
+          <t>81016; 118496</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$preocupacion-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,96</t>
+          <t>3,84; 9,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,47</t>
+          <t>3,62; 8,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 12,68</t>
+          <t>4,54; 12,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,0; 12,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,85</t>
+          <t>1,3; 11,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 27,16</t>
+          <t>5,06; 26,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,32</t>
+          <t>3,37; 8,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,6</t>
+          <t>3,75; 8,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 13,11</t>
+          <t>5,79; 12,81</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,2</t>
+          <t>5,74; 13,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,59</t>
+          <t>6,27; 13,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,25</t>
+          <t>9,22; 17,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 16,59</t>
+          <t>6,07; 16,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 12,65</t>
+          <t>4,75; 12,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,46</t>
+          <t>3,59; 10,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,92</t>
+          <t>6,91; 13,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,32</t>
+          <t>6,24; 11,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 13,04</t>
+          <t>7,49; 13,04</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 18,75</t>
+          <t>4,49; 17,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 17,43</t>
+          <t>4,54; 16,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 27,53</t>
+          <t>10,0; 28,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 17,29</t>
+          <t>2,24; 18,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 20,5</t>
+          <t>6,01; 20,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 18,27</t>
+          <t>5,23; 18,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 14,98</t>
+          <t>4,9; 15,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 16,1</t>
+          <t>6,37; 15,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 21,28</t>
+          <t>9,04; 19,84</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,13</t>
+          <t>5,79; 10,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,9</t>
+          <t>5,88; 9,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,99</t>
+          <t>9,02; 14,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,15</t>
+          <t>5,27; 12,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,19</t>
+          <t>5,51; 11,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 11,84</t>
+          <t>5,6; 11,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,92</t>
+          <t>6,11; 9,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,75</t>
+          <t>6,39; 9,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 12,67</t>
+          <t>8,53; 12,61</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11428; 27148</t>
+          <t>11635; 27665</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14529; 35227</t>
+          <t>13462; 33191</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10760; 26604</t>
+          <t>9518; 25474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 5798</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>943; 8184</t>
+          <t>901; 7812</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1929; 10222</t>
+          <t>1905; 9827</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12095; 29239</t>
+          <t>11841; 29251</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16718; 37921</t>
+          <t>16561; 37777</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14651; 32428</t>
+          <t>14326; 31689</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12924; 31291</t>
+          <t>13613; 31202</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20361; 43778</t>
+          <t>21789; 45729</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26764; 52113</t>
+          <t>27852; 51465</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9410; 25089</t>
+          <t>9178; 24971</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11395; 30372</t>
+          <t>11393; 29400</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6728; 21025</t>
+          <t>7225; 21387</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26395; 50176</t>
+          <t>26816; 51297</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36933; 66521</t>
+          <t>36701; 65981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36874; 65585</t>
+          <t>37673; 65621</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4653; 15834</t>
+          <t>3790; 15038</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4292; 16778</t>
+          <t>4368; 15795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8829; 24667</t>
+          <t>8964; 25805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1151; 8881</t>
+          <t>1153; 9674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4137; 15864</t>
+          <t>4650; 15857</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5056; 17371</t>
+          <t>4976; 17431</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6775; 20349</t>
+          <t>6658; 21123</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11096; 27953</t>
+          <t>11068; 27561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16697; 39307</t>
+          <t>16690; 36645</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35340; 63240</t>
+          <t>36141; 63195</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48425; 80815</t>
+          <t>48021; 80630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55773; 90145</t>
+          <t>54265; 88587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12250; 30475</t>
+          <t>13218; 31847</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20743; 43260</t>
+          <t>21302; 45371</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18750; 39519</t>
+          <t>18675; 39360</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52820; 86850</t>
+          <t>53517; 85331</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76378; 117202</t>
+          <t>76889; 116045</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81016; 118496</t>
+          <t>79798; 117903</t>
         </is>
       </c>
     </row>
